--- a/Agrotechnika_excel_files/Agrotechnika_vállalások.xlsx
+++ b/Agrotechnika_excel_files/Agrotechnika_vállalások.xlsx
@@ -507,7 +507,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>nem</t>
+          <t>igen</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
